--- a/Design-Files/Pukk-Display-Module-v1.0/BOM/JLCPCB-BOM-Pukk-Display-Module-v1.0.xlsx
+++ b/Design-Files/Pukk-Display-Module-v1.0/BOM/JLCPCB-BOM-Pukk-Display-Module-v1.0.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="217">
   <si>
     <t>Comment</t>
   </si>
@@ -184,9 +184,6 @@
   </si>
   <si>
     <t>ST1L05APU33R</t>
-  </si>
-  <si>
-    <t>DF40C-30DP-0.4V(51)</t>
   </si>
   <si>
     <t>SN74HC14QDRQ1</t>
@@ -1132,13 +1129,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -1146,13 +1143,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1160,13 +1157,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1174,13 +1171,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1188,13 +1185,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1202,13 +1199,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1216,13 +1213,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1230,13 +1227,13 @@
         <v>5</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1244,13 +1241,13 @@
         <v>7</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1258,13 +1255,13 @@
         <v>2</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1272,13 +1269,13 @@
         <v>4</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1286,13 +1283,13 @@
         <v>3</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1300,13 +1297,13 @@
         <v>8</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1314,13 +1311,13 @@
         <v>9</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1328,13 +1325,13 @@
         <v>4</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1342,13 +1339,13 @@
         <v>2</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -1356,13 +1353,13 @@
         <v>10</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -1370,13 +1367,13 @@
         <v>7</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1384,13 +1381,13 @@
         <v>11</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="24" x14ac:dyDescent="0.25">
@@ -1398,13 +1395,13 @@
         <v>12</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1412,13 +1409,13 @@
         <v>13</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1426,13 +1423,13 @@
         <v>14</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="24" x14ac:dyDescent="0.25">
@@ -1440,13 +1437,13 @@
         <v>15</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1454,13 +1451,13 @@
         <v>16</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1468,13 +1465,13 @@
         <v>17</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1482,13 +1479,13 @@
         <v>18</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -1496,13 +1493,13 @@
         <v>19</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -1510,13 +1507,13 @@
         <v>20</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -1524,13 +1521,13 @@
         <v>21</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -1538,13 +1535,13 @@
         <v>22</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>22</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1552,13 +1549,13 @@
         <v>23</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C31" s="7" t="s">
         <v>23</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1566,13 +1563,13 @@
         <v>24</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>24</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -1580,13 +1577,13 @@
         <v>25</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C33" s="7" t="s">
         <v>25</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -1594,13 +1591,13 @@
         <v>26</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C34" s="5">
         <v>302</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -1608,13 +1605,13 @@
         <v>27</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -1622,13 +1619,13 @@
         <v>28</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -1636,13 +1633,13 @@
         <v>29</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -1650,13 +1647,13 @@
         <v>30</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -1664,13 +1661,13 @@
         <v>31</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -1678,13 +1675,13 @@
         <v>32</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -1692,13 +1689,13 @@
         <v>33</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -1706,13 +1703,13 @@
         <v>34</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -1720,13 +1717,13 @@
         <v>35</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -1734,13 +1731,13 @@
         <v>36</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -1748,13 +1745,13 @@
         <v>37</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="24" x14ac:dyDescent="0.25">
@@ -1762,13 +1759,13 @@
         <v>34</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -1776,13 +1773,13 @@
         <v>38</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -1790,13 +1787,13 @@
         <v>39</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -1804,13 +1801,13 @@
         <v>40</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -1818,13 +1815,13 @@
         <v>41</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -1832,13 +1829,13 @@
         <v>39</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -1846,13 +1843,13 @@
         <v>42</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -1860,13 +1857,13 @@
         <v>43</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -1874,13 +1871,13 @@
         <v>44</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
@@ -1888,13 +1885,13 @@
         <v>45</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -1902,13 +1899,13 @@
         <v>46</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C56" s="5" t="s">
         <v>46</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -1916,13 +1913,13 @@
         <v>47</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C57" s="7" t="s">
         <v>47</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="24" x14ac:dyDescent="0.25">
@@ -1930,13 +1927,13 @@
         <v>48</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
@@ -1944,13 +1941,13 @@
         <v>49</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -1958,13 +1955,13 @@
         <v>50</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
@@ -1972,13 +1969,13 @@
         <v>51</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
@@ -1986,13 +1983,13 @@
         <v>52</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C62" s="5" t="s">
         <v>52</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
@@ -2000,13 +1997,13 @@
         <v>53</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
@@ -2014,41 +2011,41 @@
         <v>54</v>
       </c>
       <c r="B64" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C64" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D64" s="4" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="B65" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="C64" s="5" t="s">
+      <c r="C65" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="D64" s="4" t="s">
+      <c r="D65" s="6" t="s">
         <v>209</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A65" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B65" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="C65" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="D65" s="6" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
   </sheetData>
